--- a/output/pdf_financials_xlsx/LBNK.xlsx
+++ b/output/pdf_financials_xlsx/LBNK.xlsx
@@ -2492,19 +2492,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>5.343615</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.730517</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.235931</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>5.200156</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>6.767579</v>
       </c>
     </row>
     <row r="93">
@@ -4169,7 +4169,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -4655,7 +4659,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -4979,7 +4987,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>5.343615</v>
       </c>

--- a/output/pdf_financials_xlsx/LBNK.xlsx
+++ b/output/pdf_financials_xlsx/LBNK.xlsx
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.003284</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.044765</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.118763</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.330812</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0.005301</v>
@@ -1019,16 +1019,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-6.105933</v>
+        <v>-6.109217</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.463716</v>
+        <v>-3.508481</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-6.968586</v>
+        <v>-7.087349</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.752164</v>
+        <v>-5.082976</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-4.757465</v>
@@ -1063,16 +1063,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-6.105933</v>
+        <v>-6.109217</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.463716</v>
+        <v>-3.508481</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-6.968586</v>
+        <v>-7.087349</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.707792</v>
+        <v>-5.038604</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-4.757465</v>
@@ -8988,7 +8988,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">

--- a/output/pdf_financials_xlsx/LBNK.xlsx
+++ b/output/pdf_financials_xlsx/LBNK.xlsx
@@ -562,16 +562,16 @@
         <v>0.511965</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.758744</v>
+        <v>0.920744</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.481608</v>
+        <v>1.735275</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2.628403</v>
+        <v>2.843403</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.298961</v>
+        <v>1.406961</v>
       </c>
     </row>
     <row r="8">
@@ -8192,7 +8192,11 @@
           <t>Directors’ fees 13</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -9975,7 +9979,11 @@
           <t>Directors’ fees 12</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -10875,7 +10883,11 @@
           <t>Directors’ fees 8</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
